--- a/data/trans_dic/P21D_3_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P21D_3_R-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos</t>
+          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 1,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,48</t>
+          <t>0,0; 3,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,65</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,56</t>
+          <t>0,0; 0,65</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,32</t>
+          <t>0,03; 0,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,23</t>
+          <t>0,02; 0,2</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos</t>
+          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1921</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1036</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1392</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2517</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4247</t>
+          <t>0; 4362</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3905</t>
+          <t>0; 4588</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1596</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2330</t>
+          <t>0; 3116</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2827</t>
+          <t>0; 3491</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2054</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1696</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1816</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1243</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 835</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1002</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4375</t>
+          <t>0; 4148</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1059</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3894</t>
+          <t>0; 4537</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 2092</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 3148</t>
+          <t>0; 4403</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3483</t>
+          <t>0; 3993</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3183</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 1294</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 2038</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 4574</t>
+          <t>0; 4438</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>521; 5175</t>
+          <t>558; 5563</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>744; 7418</t>
+          <t>614; 6434</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_3_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P21D_3_R-Provincia-trans_dic.xlsx
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,3</t>
+          <t>0,0; 3,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 1,87</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,27</t>
+          <t>0,0; 0,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,35</t>
+          <t>0,03; 0,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>749</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>749</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4362</t>
+          <t>0; 3809</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4588</t>
+          <t>0; 4162</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>561</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>561</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3116</t>
+          <t>0; 3100</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3491</t>
+          <t>0; 3169</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4148</t>
+          <t>0; 4360</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4537</t>
+          <t>0; 4487</t>
         </is>
       </c>
     </row>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4403</t>
+          <t>0; 3521</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3993</t>
+          <t>0; 4079</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2759</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 4438</t>
+          <t>0; 4551</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>558; 5563</t>
+          <t>564; 5521</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>614; 6434</t>
+          <t>705; 6677</t>
         </is>
       </c>
     </row>
